--- a/maintenance_forms/018_ice_cream_freezer_maintenance_order_form--maintenance_forms.xlsx
+++ b/maintenance_forms/018_ice_cream_freezer_maintenance_order_form--maintenance_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -757,8 +757,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -820,12 +820,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'scheduled',_'label':_'scheduled',_'type':_'checkbox'}</t>
+          <t>scheduled</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Scheduled', 'label': 'Scheduled', 'type': 'checkbox'}</t>
+          <t>Scheduled</t>
         </is>
       </c>
     </row>
@@ -837,12 +837,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'urgent',_'label':_'urgent',_'type':_'checkbox'}</t>
+          <t>urgent</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Urgent', 'label': 'Urgent', 'type': 'checkbox'}</t>
+          <t>Urgent</t>
         </is>
       </c>
     </row>
@@ -854,12 +854,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'repair',_'label':_'repair',_'type':_'checkbox'}</t>
+          <t>repair</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'repair', 'label': 'Repair', 'type': 'checkbox'}</t>
+          <t>Repair</t>
         </is>
       </c>
     </row>
@@ -871,12 +871,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'maintenance',_'label':_'maintenance',_'type':_'checkbox'}</t>
+          <t>maintenance</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'maintenance', 'label': 'Maintenance', 'type': 'checkbox'}</t>
+          <t>Maintenance</t>
         </is>
       </c>
     </row>
@@ -888,12 +888,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'pending',_'label':_'pending',_'type':_'checkbox'}</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'pending', 'label': 'Pending', 'type': 'checkbox'}</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
@@ -905,12 +905,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'active',_'label':_'active',_'type':_'checkbox'}</t>
+          <t>active</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'active', 'label': 'Active', 'type': 'checkbox'}</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
@@ -922,12 +922,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'closed',_'label':_'closed',_'type':_'checkbox'}</t>
+          <t>closed</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'closed', 'label': 'Closed', 'type': 'checkbox'}</t>
+          <t>Closed</t>
         </is>
       </c>
     </row>
